--- a/kanji.xlsx
+++ b/kanji.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\507042-ichi\iCloudDrive\Ichikawa\作成アプリ\漢字ドリル\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1JeTC735xH0AYKEZHrlVrGX49WCae_-Md\00-WORK\100-Projects\#作成アプリ\漢字ドリル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFD878F-0D44-4BEA-934C-DCC195E7B5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890F1B9D-8AC2-435F-B947-5008951E945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2010" windowWidth="32520" windowHeight="16610" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
+    <workbookView xWindow="9030" yWindow="0" windowWidth="26010" windowHeight="20880" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6877" uniqueCount="3713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6878" uniqueCount="3714">
   <si>
     <t>教材名</t>
     <rPh sb="0" eb="3">
@@ -20691,6 +20691,10 @@
   <si>
     <t>こぎって</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>じょ/せい/よう</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -29481,6 +29485,9 @@
       <c r="E363" t="s">
         <v>1489</v>
       </c>
+      <c r="F363" t="s">
+        <v>3713</v>
+      </c>
       <c r="G363" s="1" t="s">
         <v>1008</v>
       </c>

--- a/kanji.xlsx
+++ b/kanji.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1JeTC735xH0AYKEZHrlVrGX49WCae_-Md\00-WORK\100-Projects\#作成アプリ\漢字ドリル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890F1B9D-8AC2-435F-B947-5008951E945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB7B2BE-D2E2-4D91-B399-9068E07A8B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9030" yWindow="0" windowWidth="26010" windowHeight="20880" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
+    <workbookView xWindow="1520" yWindow="0" windowWidth="26010" windowHeight="20880" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6878" uniqueCount="3714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6879" uniqueCount="3716">
   <si>
     <t>教材名</t>
     <rPh sb="0" eb="3">
@@ -20694,6 +20694,14 @@
   </si>
   <si>
     <t>じょ/せい/よう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ぎん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>し/よう/ちゅう</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -29747,6 +29755,9 @@
       <c r="E374" t="s">
         <v>160</v>
       </c>
+      <c r="F374" t="s">
+        <v>3715</v>
+      </c>
       <c r="G374" s="1" t="s">
         <v>1019</v>
       </c>
@@ -30004,7 +30015,7 @@
         <v>1034</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>344</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.6">
